--- a/site/exports/Tennessee_Surplus_Feed.xlsx
+++ b/site/exports/Tennessee_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>

--- a/site/exports/Tennessee_Surplus_Feed.xlsx
+++ b/site/exports/Tennessee_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>

--- a/site/exports/Tennessee_Surplus_Feed.xlsx
+++ b/site/exports/Tennessee_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://chanceryclerkandmaster.nashville.gov/</t>
+          <t>https://chanceryclerkandmaster.nashville.gov/case-search?docket=2024-TN-002190</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://chancery.shelbycountytn.gov/</t>
+          <t>https://chancery.shelbycountytn.gov/case-search?docket=2024-TN-004110</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://chanceryclerkandmaster.nashville.gov/</t>
+          <t>https://chanceryclerkandmaster.nashville.gov/case-search?docket=2024-TN-002840</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://chancery.shelbycountytn.gov/</t>
+          <t>https://chancery.shelbycountytn.gov/case-search?docket=2024-TN-004550</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>

--- a/site/exports/Tennessee_Surplus_Feed.xlsx
+++ b/site/exports/Tennessee_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://chanceryclerkandmaster.nashville.gov/case-search?docket=2024-TN-002190</t>
+          <t>https://chanceryclerkandmaster.nashville.gov/</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://chancery.shelbycountytn.gov/case-search?docket=2024-TN-004110</t>
+          <t>https://chancery.shelbycountytn.gov/</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://chanceryclerkandmaster.nashville.gov/case-search?docket=2024-TN-002840</t>
+          <t>https://chanceryclerkandmaster.nashville.gov/</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://chancery.shelbycountytn.gov/case-search?docket=2024-TN-004550</t>
+          <t>https://chancery.shelbycountytn.gov/</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>

--- a/site/exports/Tennessee_Surplus_Feed.xlsx
+++ b/site/exports/Tennessee_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://chanceryclerkandmaster.nashville.gov/</t>
+          <t>https://chanceryclerkandmaster.nashville.gov/cases/public-records-search/?docket=2024-TN-002190</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://chancery.shelbycountytn.gov/</t>
+          <t>https://www.shelbycountytn.gov/222/Chancery-Court?docket=2024-TN-004110</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://chanceryclerkandmaster.nashville.gov/</t>
+          <t>https://chanceryclerkandmaster.nashville.gov/cases/public-records-search/?docket=2024-TN-002840</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://chancery.shelbycountytn.gov/</t>
+          <t>https://www.shelbycountytn.gov/222/Chancery-Court?docket=2024-TN-004550</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>

--- a/site/exports/Tennessee_Surplus_Feed.xlsx
+++ b/site/exports/Tennessee_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>

--- a/site/exports/Tennessee_Surplus_Feed.xlsx
+++ b/site/exports/Tennessee_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>

--- a/site/exports/Tennessee_Surplus_Feed.xlsx
+++ b/site/exports/Tennessee_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>

--- a/site/exports/Tennessee_Surplus_Feed.xlsx
+++ b/site/exports/Tennessee_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>

--- a/site/exports/Tennessee_Surplus_Feed.xlsx
+++ b/site/exports/Tennessee_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>

--- a/site/exports/Tennessee_Surplus_Feed.xlsx
+++ b/site/exports/Tennessee_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>

--- a/site/exports/Tennessee_Surplus_Feed.xlsx
+++ b/site/exports/Tennessee_Surplus_Feed.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,131 +413,146 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y5"/>
+  <dimension ref="A1:AB28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>County</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Parcel_ID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Case_or_TaxDeed_No</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Owner_Name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Entity_Type</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Is_Individual</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Heir_Search_Recommended</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Property_Address</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Property_Type</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Surplus_Balance_USD</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Statutory_Fee_Rate</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Est_Finder_Fee_USD</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Opportunity_Tier</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Sale_Date</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Days_Remaining_To_Claim</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Claim_Urgency_Tier</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Claim_Deadline_Date</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Statutory_Deadline_Window</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Clerk_Verification_URL</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Verify_Note</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Source_URL</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
         <is>
           <t>Governing_Statute</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Statute_Citation</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Record_Type</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>TYPE</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Retrieved_At</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Enriched_Timestamp</t>
         </is>
@@ -568,42 +571,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>09402002900</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2024-TN-002190</t>
+          <t>24-0388-I-09402002900</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FRANKLIN &amp; JUDITH MERCER</t>
+          <t>Estate and Heirs of Woodard, Helen M &amp; Pope</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Individual / Estate</t>
+          <t>Estate / Deceased</t>
         </is>
       </c>
       <c r="G2" t="b">
         <v>1</v>
       </c>
       <c r="H2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2418 WEST END AVE NASHVILLE TN 37203</t>
+          <t>Parcel 09402002900, Metropolitan Nashville &amp; Davidson County, TN</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Single Family Residential</t>
+          <t>Vacant Land / Acreage</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>126000</v>
+        <v>248942.87</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -611,7 +614,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>25200</v>
+        <v>49788.57</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -620,55 +623,70 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>50</v>
+        <v>-18</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Tier 2: Priority Window (45–120 Days)</t>
+          <t>Statutory window may have passed — confirm with clerk</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>Chancery Court Motion Procedure (T.C.A. § 67-5-2501)</t>
+          <t>1 year from order confirming sale (T.C.A. § 67-5-2702)</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://chanceryclerkandmaster.nashville.gov/cases/public-records-search/?docket=2024-TN-002190</t>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf#search=09402002900</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>T.C.A. § 67-5-2501</t>
+          <t>Listed on Davidson County Chancery Court Excess Proceeds PDF — Case 24-0388-I, Parcel 09402002900</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>T.C.A. § 67-5-2501</t>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Tax Deed Surplus</t>
+          <t>T.C.A. § 67-5-2702</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>TAX_DEED</t>
+          <t>T.C.A. § 67-5-2702</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-16 11:20:53</t>
+          <t>Tax Sale Excess Proceeds</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>EXCESS_PROCEEDS</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>2026-10-16T13:56:13Z</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>2026-10-16 09:56:13</t>
         </is>
       </c>
     </row>
@@ -680,22 +698,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Shelby</t>
+          <t>Davidson</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>072060N00100CO</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2024-TN-004110</t>
+          <t>25-0490-II-072060N00100CO</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LAWRENCE &amp; TINA BENNETT</t>
+          <t>Marckwardt, Thomas Hunter &amp; Kimberly P</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -711,16 +729,16 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1720 POPLAR AVE MEMPHIS TN 38104</t>
+          <t>Parcel 072060N00100CO, Metropolitan Nashville &amp; Davidson County, TN</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Single Family Residential</t>
+          <t>Vacant Land / Acreage</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>102000</v>
+        <v>205482.52</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -728,7 +746,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>20400</v>
+        <v>41096.5</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -737,55 +755,70 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>50</v>
+        <v>319</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Tier 2: Priority Window (45–120 Days)</t>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2027-09-01</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>Chancery Court Motion Procedure (T.C.A. § 67-5-2501)</t>
+          <t>1 year from order confirming sale (T.C.A. § 67-5-2702)</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://www.shelbycountytn.gov/222/Chancery-Court?docket=2024-TN-004110</t>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf#search=072060N00100CO</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>T.C.A. § 67-5-2501</t>
+          <t>Listed on Davidson County Chancery Court Excess Proceeds PDF — Case 25-0490-II, Parcel 072060N00100CO</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>T.C.A. § 67-5-2501</t>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Tax Deed Surplus</t>
+          <t>T.C.A. § 67-5-2702</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>TAX_DEED</t>
+          <t>T.C.A. § 67-5-2702</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-16 11:20:53</t>
+          <t>Tax Sale Excess Proceeds</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>EXCESS_PROCEEDS</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-10-16T13:56:13Z</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>2026-10-16 09:56:13</t>
         </is>
       </c>
     </row>
@@ -802,42 +835,42 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>09213033100</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2024-TN-002840</t>
+          <t>23-0416-IV-09213033100</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ESTATE OF GLORIA CHANDLER</t>
+          <t>Mayes, Charles E.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Estate / Deceased</t>
+          <t>Individual / Estate</t>
         </is>
       </c>
       <c r="G4" t="b">
         <v>1</v>
       </c>
       <c r="H4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3904 GALLATIN PIKE NASHVILLE TN 37216</t>
+          <t>Parcel 09213033100, Metropolitan Nashville &amp; Davidson County, TN</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Single Family Residential</t>
+          <t>Vacant Land / Acreage</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>84500</v>
+        <v>203147.52</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -845,7 +878,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>16900</v>
+        <v>40629.5</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -854,55 +887,70 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>50</v>
+        <v>-441</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Tier 2: Priority Window (45–120 Days)</t>
+          <t>Statutory window may have passed — confirm with clerk</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>Chancery Court Motion Procedure (T.C.A. § 67-5-2501)</t>
+          <t>1 year from order confirming sale (T.C.A. § 67-5-2702)</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://chanceryclerkandmaster.nashville.gov/cases/public-records-search/?docket=2024-TN-002840</t>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf#search=09213033100</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>T.C.A. § 67-5-2501</t>
+          <t>Listed on Davidson County Chancery Court Excess Proceeds PDF — Case 23-0416-IV, Parcel 09213033100</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>T.C.A. § 67-5-2501</t>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Tax Deed Surplus</t>
+          <t>T.C.A. § 67-5-2702</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>TAX_DEED</t>
+          <t>T.C.A. § 67-5-2702</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-16 11:20:53</t>
+          <t>Tax Sale Excess Proceeds</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>EXCESS_PROCEEDS</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-10-16T13:56:13Z</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>2026-10-16 09:56:13</t>
         </is>
       </c>
     </row>
@@ -914,22 +962,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Shelby</t>
+          <t>Davidson</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>01816006300</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2024-TN-004550</t>
+          <t>24-0388-I-01816006300</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ESTATE OF BERNARD HAYES</t>
+          <t>Estate and Heirs of Parker, Randall</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -945,16 +993,16 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4810 PARK AVE MEMPHIS TN 38117</t>
+          <t>Parcel 01816006300, Metropolitan Nashville &amp; Davidson County, TN</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Single Family Residential</t>
+          <t>Vacant Land / Acreage</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>71800</v>
+        <v>157744.3</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -962,7 +1010,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>14360</v>
+        <v>31548.86</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -971,55 +1019,3106 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>50</v>
+        <v>-18</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Tier 2: Priority Window (45–120 Days)</t>
+          <t>Statutory window may have passed — confirm with clerk</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Chancery Court Motion Procedure (T.C.A. § 67-5-2501)</t>
+          <t>1 year from order confirming sale (T.C.A. § 67-5-2702)</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://www.shelbycountytn.gov/222/Chancery-Court?docket=2024-TN-004550</t>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf#search=01816006300</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>T.C.A. § 67-5-2501</t>
+          <t>Listed on Davidson County Chancery Court Excess Proceeds PDF — Case 24-0388-I, Parcel 01816006300</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>T.C.A. § 67-5-2501</t>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Tax Deed Surplus</t>
+          <t>T.C.A. § 67-5-2702</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>TAX_DEED</t>
+          <t>T.C.A. § 67-5-2702</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-16 11:20:53</t>
+          <t>Tax Sale Excess Proceeds</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>EXCESS_PROCEEDS</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-16T13:56:13Z</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>2026-10-16 09:56:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Davidson</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>051150C00700CO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>25-0490-II-051150C00700CO</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Wallace, Melissa</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="G6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Parcel 051150C00700CO, Metropolitan Nashville &amp; Davidson County, TN</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Vacant Land / Acreage</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>157388.41</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>31477.68</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>319</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>2027-09-01</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>1 year from order confirming sale (T.C.A. § 67-5-2702)</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf#search=051150C00700CO</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Listed on Davidson County Chancery Court Excess Proceeds PDF — Case 25-0490-II, Parcel 051150C00700CO</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2702</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2702</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Tax Sale Excess Proceeds</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>EXCESS_PROCEEDS</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-16T13:56:13Z</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>2026-10-16 09:56:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Davidson</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>051100E01800CO</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>25-0490-II-051100E01800CO</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Gupton, Marsha E</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="G7" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Parcel 051100E01800CO, Metropolitan Nashville &amp; Davidson County, TN</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Vacant Land / Acreage</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>106024.97</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>21204.99</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>319</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>2027-09-01</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>1 year from order confirming sale (T.C.A. § 67-5-2702)</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf#search=051100E01800CO</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Listed on Davidson County Chancery Court Excess Proceeds PDF — Case 25-0490-II, Parcel 051100E01800CO</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2702</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2702</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Tax Sale Excess Proceeds</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>EXCESS_PROCEEDS</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-16T13:56:13Z</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>2026-10-16 09:56:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Davidson</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>10803019800</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>25-0490-II-10803019800</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Raisane, Thomas D. &amp; Pennington, Deborah</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="G8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Parcel 10803019800, Metropolitan Nashville &amp; Davidson County, TN</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Vacant Land / Acreage</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>84881.28</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>16976.26</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>140</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>2027-03-06</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>1 year from order confirming sale (T.C.A. § 67-5-2702)</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf#search=10803019800</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Listed on Davidson County Chancery Court Excess Proceeds PDF — Case 25-0490-II, Parcel 10803019800</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2702</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2702</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Tax Sale Excess Proceeds</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>EXCESS_PROCEEDS</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-16T13:56:13Z</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>2026-10-16 09:56:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Davidson</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>107130A04000CO</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>25-0490-II-107130A04000CO</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Manning, Walter &amp; Delilah &amp; Karah J</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="G9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Parcel 107130A04000CO, Metropolitan Nashville &amp; Davidson County, TN</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Vacant Land / Acreage</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>78923.67999999999</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>15784.74</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>319</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>2027-09-01</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>1 year from order confirming sale (T.C.A. § 67-5-2702)</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf#search=107130A04000CO</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Listed on Davidson County Chancery Court Excess Proceeds PDF — Case 25-0490-II, Parcel 107130A04000CO</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2702</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2702</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Tax Sale Excess Proceeds</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>EXCESS_PROCEEDS</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-16T13:56:13Z</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>2026-10-16 09:56:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Davidson</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>043100B10200CO</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>25-0490-II-043100B10200CO</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>McClain, Eugenia</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="G10" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Parcel 043100B10200CO, Metropolitan Nashville &amp; Davidson County, TN</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Vacant Land / Acreage</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>71852.92</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>14370.58</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>319</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>2027-09-01</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>1 year from order confirming sale (T.C.A. § 67-5-2702)</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf#search=043100B10200CO</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Listed on Davidson County Chancery Court Excess Proceeds PDF — Case 25-0490-II, Parcel 043100B10200CO</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2702</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2702</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Tax Sale Excess Proceeds</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>EXCESS_PROCEEDS</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-16T13:56:13Z</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>2026-10-16 09:56:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Davidson</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>053120B03600CO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>25-0490-II-053120B03600CO</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Amin, Siddharth</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="G11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Parcel 053120B03600CO, Metropolitan Nashville &amp; Davidson County, TN</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Vacant Land / Acreage</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>69953.44</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>13990.69</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>319</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>2027-09-01</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>1 year from order confirming sale (T.C.A. § 67-5-2702)</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf#search=053120B03600CO</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Listed on Davidson County Chancery Court Excess Proceeds PDF — Case 25-0490-II, Parcel 053120B03600CO</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2702</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2702</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Tax Sale Excess Proceeds</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>EXCESS_PROCEEDS</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-16T13:56:13Z</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>2026-10-16 09:56:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Davidson</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>04307003500</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>23-0416-IV-04307003500</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Estate and Heirs of Maynard, Brownie Lee</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Estate / Deceased</t>
+        </is>
+      </c>
+      <c r="G12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Parcel 04307003500, Metropolitan Nashville &amp; Davidson County, TN</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Vacant Land / Acreage</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>66829.17</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>13365.83</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>-441</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Statutory window may have passed — confirm with clerk</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>1 year from order confirming sale (T.C.A. § 67-5-2702)</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf#search=04307003500</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Listed on Davidson County Chancery Court Excess Proceeds PDF — Case 23-0416-IV, Parcel 04307003500</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2702</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2702</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Tax Sale Excess Proceeds</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>EXCESS_PROCEEDS</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-16T13:56:13Z</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>2026-10-16 09:56:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Davidson</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>053120B03500CO</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>25-0490-II-053120B03500CO</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Amin, Siddharth</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="G13" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" t="b">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Parcel 053120B03500CO, Metropolitan Nashville &amp; Davidson County, TN</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Vacant Land / Acreage</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>61953.44</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>12390.69</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>319</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>2027-09-01</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>1 year from order confirming sale (T.C.A. § 67-5-2702)</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf#search=053120B03500CO</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Listed on Davidson County Chancery Court Excess Proceeds PDF — Case 25-0490-II, Parcel 053120B03500CO</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2702</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2702</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Tax Sale Excess Proceeds</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>EXCESS_PROCEEDS</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-16T13:56:13Z</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>2026-10-16 09:56:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Davidson</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>04900036700</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>22-0464-III-04900036700</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Estate and Heirs of Meadows, James A &amp; Onether I.</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Estate / Deceased</t>
+        </is>
+      </c>
+      <c r="G14" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Parcel 04900036700, Metropolitan Nashville &amp; Davidson County, TN</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Vacant Land / Acreage</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>60054.63</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>12010.93</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2023-08-11</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>-798</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Statutory window may have passed — confirm with clerk</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>2024-08-10</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>1 year from order confirming sale (T.C.A. § 67-5-2702)</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf#search=04900036700</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Listed on Davidson County Chancery Court Excess Proceeds PDF — Case 22-0464-III, Parcel 04900036700</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2702</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2702</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Tax Sale Excess Proceeds</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>EXCESS_PROCEEDS</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-16T13:56:13Z</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>2026-10-16 09:56:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Davidson</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>164080A04400CO</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>24-0388-I-164080A04400CO</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Infinity Home Builders, G.P.</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="G15" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Parcel 164080A04400CO, Metropolitan Nashville &amp; Davidson County, TN</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Vacant Land / Acreage</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>51019.95</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>10203.99</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>-18</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Statutory window may have passed — confirm with clerk</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1 year from order confirming sale (T.C.A. § 67-5-2702)</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf#search=164080A04400CO</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Listed on Davidson County Chancery Court Excess Proceeds PDF — Case 24-0388-I, Parcel 164080A04400CO</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2702</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2702</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Tax Sale Excess Proceeds</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>EXCESS_PROCEEDS</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-16T13:56:13Z</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>2026-10-16 09:56:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Davidson</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>05307008300</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>19-360-IV-05307008300</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Weatherford, Harry Jr.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="G16" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Parcel 05307008300, Metropolitan Nashville &amp; Davidson County, TN</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Vacant Land / Acreage</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>48009.02</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>9601.799999999999</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2019-08-26</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>-2244</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Statutory window may have passed — confirm with clerk</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>2020-08-25</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>1 year from order confirming sale (T.C.A. § 67-5-2702)</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf#search=05307008300</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Listed on Davidson County Chancery Court Excess Proceeds PDF — Case 19-360-IV, Parcel 05307008300</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2702</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2702</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Tax Sale Excess Proceeds</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>EXCESS_PROCEEDS</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-16T13:56:13Z</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>2026-10-16 09:56:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Davidson</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>08112007400</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>24-0388-I-08112007400</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Stratton, Debra A</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="G17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Parcel 08112007400, Metropolitan Nashville &amp; Davidson County, TN</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Vacant Land / Acreage</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>22820.36</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>4564.07</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Tier 2: Medium Value ($10k-$25k)</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>-254</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Statutory window may have passed — confirm with clerk</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>1 year from order confirming sale (T.C.A. § 67-5-2702)</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf#search=08112007400</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Listed on Davidson County Chancery Court Excess Proceeds PDF — Case 24-0388-I, Parcel 08112007400</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2702</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2702</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Tax Sale Excess Proceeds</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>EXCESS_PROCEEDS</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-10-16T13:56:13Z</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>2026-10-16 09:56:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Davidson</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>10100020100</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>25-0490-II-10100020100</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Williams, Searra &amp; Lindsley, Marquita</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="G18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" t="b">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Parcel 10100020100, Metropolitan Nashville &amp; Davidson County, TN</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Vacant Land / Acreage</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>22546.79</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>4509.36</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Tier 2: Medium Value ($10k-$25k)</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>319</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>2027-09-01</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1 year from order confirming sale (T.C.A. § 67-5-2702)</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf#search=10100020100</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Listed on Davidson County Chancery Court Excess Proceeds PDF — Case 25-0490-II, Parcel 10100020100</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2702</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2702</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Tax Sale Excess Proceeds</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>EXCESS_PROCEEDS</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-10-16T13:56:13Z</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>2026-10-16 09:56:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Davidson</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>14900034000</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>24-0388-I-14900034000</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Zaver, Vinod T &amp; Manglaben, V</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="G19" t="b">
+        <v>1</v>
+      </c>
+      <c r="H19" t="b">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Parcel 14900034000, Metropolitan Nashville &amp; Davidson County, TN</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Vacant Land / Acreage</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>21143.4</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>4228.68</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Tier 2: Medium Value ($10k-$25k)</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>-18</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Statutory window may have passed — confirm with clerk</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>1 year from order confirming sale (T.C.A. § 67-5-2702)</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf#search=14900034000</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Listed on Davidson County Chancery Court Excess Proceeds PDF — Case 24-0388-I, Parcel 14900034000</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2702</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2702</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Tax Sale Excess Proceeds</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>EXCESS_PROCEEDS</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-10-16T13:56:13Z</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>2026-10-16 09:56:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Davidson</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>14714018100</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>22-0464-III-14714018100</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sundance of Nashville LTD</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="G20" t="b">
+        <v>1</v>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Parcel 14714018100, Metropolitan Nashville &amp; Davidson County, TN</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Vacant Land / Acreage</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>17501.33</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>3500.27</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Tier 2: Medium Value ($10k-$25k)</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2023-03-10</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>-952</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Statutory window may have passed — confirm with clerk</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>2024-03-09</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1 year from order confirming sale (T.C.A. § 67-5-2702)</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf#search=14714018100</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Listed on Davidson County Chancery Court Excess Proceeds PDF — Case 22-0464-III, Parcel 14714018100</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2702</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2702</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Tax Sale Excess Proceeds</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>EXCESS_PROCEEDS</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-10-16T13:56:13Z</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>2026-10-16 09:56:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Davidson</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>01700026000</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>25-0490-II-01700026000</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Davis, Jeanette (Le) &amp; Davis, Tyson</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="G21" t="b">
+        <v>1</v>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Parcel 01700026000, Metropolitan Nashville &amp; Davidson County, TN</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Vacant Land / Acreage</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>8423.98</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>1684.8</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Tier 3: Standard Value ($2.5k-$10k)</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>319</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>2027-09-01</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>1 year from order confirming sale (T.C.A. § 67-5-2702)</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf#search=01700026000</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Listed on Davidson County Chancery Court Excess Proceeds PDF — Case 25-0490-II, Parcel 01700026000</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2702</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2702</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Tax Sale Excess Proceeds</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>EXCESS_PROCEEDS</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-10-16T13:56:13Z</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>2026-10-16 09:56:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Davidson</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>02200014100</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>24-0388-I-02200014100</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Davidson, Genevieve Ann</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="G22" t="b">
+        <v>1</v>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Parcel 02200014100, Metropolitan Nashville &amp; Davidson County, TN</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Vacant Land / Acreage</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>6455.83</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>1291.17</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Tier 3: Standard Value ($2.5k-$10k)</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>-18</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Statutory window may have passed — confirm with clerk</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>1 year from order confirming sale (T.C.A. § 67-5-2702)</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf#search=02200014100</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Listed on Davidson County Chancery Court Excess Proceeds PDF — Case 24-0388-I, Parcel 02200014100</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2702</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2702</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>Tax Sale Excess Proceeds</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>EXCESS_PROCEEDS</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-10-16T13:56:13Z</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>2026-10-16 09:56:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Davidson</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>09413005200</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>23-0416-IV-09413005200</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Estate and Heirs of Howse, Margaret L</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Estate / Deceased</t>
+        </is>
+      </c>
+      <c r="G23" t="b">
+        <v>1</v>
+      </c>
+      <c r="H23" t="b">
+        <v>1</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Parcel 09413005200, Metropolitan Nashville &amp; Davidson County, TN</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Vacant Land / Acreage</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>6408.49</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>1281.7</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Tier 3: Standard Value ($2.5k-$10k)</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>-441</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Statutory window may have passed — confirm with clerk</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>1 year from order confirming sale (T.C.A. § 67-5-2702)</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf#search=09413005200</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Listed on Davidson County Chancery Court Excess Proceeds PDF — Case 23-0416-IV, Parcel 09413005200</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2702</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2702</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>Tax Sale Excess Proceeds</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>EXCESS_PROCEEDS</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-10-16T13:56:13Z</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>2026-10-16 09:56:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Davidson</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>08415005400</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>24-0388-I-08415005400</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Estate and Heirs of Martin, William J et ux</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Estate / Deceased</t>
+        </is>
+      </c>
+      <c r="G24" t="b">
+        <v>1</v>
+      </c>
+      <c r="H24" t="b">
+        <v>1</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Parcel 08415005400, Metropolitan Nashville &amp; Davidson County, TN</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Vacant Land / Acreage</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>6303.6</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>1260.72</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Tier 3: Standard Value ($2.5k-$10k)</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>-18</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Statutory window may have passed — confirm with clerk</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>1 year from order confirming sale (T.C.A. § 67-5-2702)</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf#search=08415005400</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Listed on Davidson County Chancery Court Excess Proceeds PDF — Case 24-0388-I, Parcel 08415005400</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2702</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2702</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>Tax Sale Excess Proceeds</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>EXCESS_PROCEEDS</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-10-16T13:56:13Z</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>2026-10-16 09:56:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Davidson</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>04115010000</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>24-0388-I-04115010000</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Estate &amp; Heirs of England, Linda &amp; Lee, Fredda</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Estate / Deceased</t>
+        </is>
+      </c>
+      <c r="G25" t="b">
+        <v>1</v>
+      </c>
+      <c r="H25" t="b">
+        <v>1</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Parcel 04115010000, Metropolitan Nashville &amp; Davidson County, TN</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Vacant Land / Acreage</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>5156.19</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>1031.24</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Tier 3: Standard Value ($2.5k-$10k)</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>-203</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Statutory window may have passed — confirm with clerk</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>1 year from order confirming sale (T.C.A. § 67-5-2702)</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf#search=04115010000</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Listed on Davidson County Chancery Court Excess Proceeds PDF — Case 24-0388-I, Parcel 04115010000</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2702</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2702</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>Tax Sale Excess Proceeds</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>EXCESS_PROCEEDS</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-10-16T13:56:13Z</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>2026-10-16 09:56:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Davidson</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>05916016200</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>23-0416-IV-05916016200</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Mims, James V. &amp; Olene H.</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="G26" t="b">
+        <v>1</v>
+      </c>
+      <c r="H26" t="b">
+        <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Parcel 05916016200, Metropolitan Nashville &amp; Davidson County, TN</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Vacant Land / Acreage</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>4333.27</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>866.65</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Tier 3: Standard Value ($2.5k-$10k)</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>-441</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Statutory window may have passed — confirm with clerk</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>1 year from order confirming sale (T.C.A. § 67-5-2702)</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf#search=05916016200</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Listed on Davidson County Chancery Court Excess Proceeds PDF — Case 23-0416-IV, Parcel 05916016200</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2702</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2702</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>Tax Sale Excess Proceeds</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>EXCESS_PROCEEDS</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-10-16T13:56:13Z</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>2026-10-16 09:56:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Davidson</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>12810020100</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>22-0464-III-12810020100</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Rainey, Kenneth &amp; Ross, Linda</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="G27" t="b">
+        <v>1</v>
+      </c>
+      <c r="H27" t="b">
+        <v>0</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Parcel 12810020100, Metropolitan Nashville &amp; Davidson County, TN</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Vacant Land / Acreage</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>3759.87</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>751.97</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Tier 3: Standard Value ($2.5k-$10k)</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2023-08-11</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>-798</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Statutory window may have passed — confirm with clerk</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>2024-08-10</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>1 year from order confirming sale (T.C.A. § 67-5-2702)</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf#search=12810020100</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Listed on Davidson County Chancery Court Excess Proceeds PDF — Case 22-0464-III, Parcel 12810020100</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2702</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2702</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>Tax Sale Excess Proceeds</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>EXCESS_PROCEEDS</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-10-16T13:56:13Z</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>2026-10-16 09:56:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Davidson</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>03100000100</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>24-0388-I-03100000100</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Hobson, Albert</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="G28" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28" t="b">
+        <v>0</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Parcel 03100000100, Metropolitan Nashville &amp; Davidson County, TN</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Vacant Land / Acreage</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>2950.62</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>590.12</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Tier 3: Standard Value ($2.5k-$10k)</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>-203</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Statutory window may have passed — confirm with clerk</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>1 year from order confirming sale (T.C.A. § 67-5-2702)</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf#search=03100000100</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Listed on Davidson County Chancery Court Excess Proceeds PDF — Case 24-0388-I, Parcel 03100000100</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>https://chanceryclerkandmaster.nashville.gov/wp-content/uploads/Excess-Proceeds-updated-10-15.pdf</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2702</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2702</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>Tax Sale Excess Proceeds</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>EXCESS_PROCEEDS</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-10-16T13:56:13Z</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>2026-10-16 09:56:13</t>
         </is>
       </c>
     </row>

--- a/site/exports/Tennessee_Surplus_Feed.xlsx
+++ b/site/exports/Tennessee_Surplus_Feed.xlsx
@@ -681,12 +681,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:56:13Z</t>
+          <t>2026-10-16T14:17:38Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-16T13:56:13Z</t>
+          <t>2026-10-16T14:17:38Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-16T13:56:13Z</t>
+          <t>2026-10-16T14:17:38Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-16T13:56:13Z</t>
+          <t>2026-10-16T14:17:38Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-16T13:56:13Z</t>
+          <t>2026-10-16T14:17:38Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1341,12 +1341,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:56:13Z</t>
+          <t>2026-10-16T14:17:38Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-16T13:56:13Z</t>
+          <t>2026-10-16T14:17:38Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1605,12 +1605,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-16T13:56:13Z</t>
+          <t>2026-10-16T14:17:38Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1737,12 +1737,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-16T13:56:13Z</t>
+          <t>2026-10-16T14:17:38Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1869,12 +1869,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-16T13:56:13Z</t>
+          <t>2026-10-16T14:17:38Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2001,12 +2001,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-16T13:56:13Z</t>
+          <t>2026-10-16T14:17:38Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2133,12 +2133,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-16T13:56:13Z</t>
+          <t>2026-10-16T14:17:38Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2265,12 +2265,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-16T13:56:13Z</t>
+          <t>2026-10-16T14:17:38Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2397,12 +2397,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-16T13:56:13Z</t>
+          <t>2026-10-16T14:17:38Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2529,12 +2529,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-16T13:56:13Z</t>
+          <t>2026-10-16T14:17:38Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2661,12 +2661,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-16T13:56:13Z</t>
+          <t>2026-10-16T14:17:38Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-16T13:56:13Z</t>
+          <t>2026-10-16T14:17:38Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2925,12 +2925,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-16T13:56:13Z</t>
+          <t>2026-10-16T14:17:38Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3057,12 +3057,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-16T13:56:13Z</t>
+          <t>2026-10-16T14:17:38Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3189,12 +3189,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-16T13:56:13Z</t>
+          <t>2026-10-16T14:17:38Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3321,12 +3321,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-16T13:56:13Z</t>
+          <t>2026-10-16T14:17:38Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3453,12 +3453,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-16T13:56:13Z</t>
+          <t>2026-10-16T14:17:38Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3585,12 +3585,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-16T13:56:13Z</t>
+          <t>2026-10-16T14:17:38Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3717,12 +3717,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-16T13:56:13Z</t>
+          <t>2026-10-16T14:17:38Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3849,12 +3849,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-16T13:56:13Z</t>
+          <t>2026-10-16T14:17:38Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3981,12 +3981,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-16T13:56:13Z</t>
+          <t>2026-10-16T14:17:38Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4113,12 +4113,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-16T13:56:13Z</t>
+          <t>2026-10-16T14:17:38Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>

--- a/site/exports/Tennessee_Surplus_Feed.xlsx
+++ b/site/exports/Tennessee_Surplus_Feed.xlsx
@@ -681,12 +681,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-16T14:17:38Z</t>
+          <t>2026-10-16T14:36:03Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-16T14:17:38Z</t>
+          <t>2026-10-16T14:36:03Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-16T14:17:38Z</t>
+          <t>2026-10-16T14:36:03Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-16T14:17:38Z</t>
+          <t>2026-10-16T14:36:03Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-16T14:17:38Z</t>
+          <t>2026-10-16T14:36:03Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1341,12 +1341,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-16T14:17:38Z</t>
+          <t>2026-10-16T14:36:03Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-16T14:17:38Z</t>
+          <t>2026-10-16T14:36:03Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1605,12 +1605,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-16T14:17:38Z</t>
+          <t>2026-10-16T14:36:03Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1737,12 +1737,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-16T14:17:38Z</t>
+          <t>2026-10-16T14:36:03Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1869,12 +1869,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-16T14:17:38Z</t>
+          <t>2026-10-16T14:36:03Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2001,12 +2001,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-16T14:17:38Z</t>
+          <t>2026-10-16T14:36:03Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2133,12 +2133,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-16T14:17:38Z</t>
+          <t>2026-10-16T14:36:03Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2265,12 +2265,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-16T14:17:38Z</t>
+          <t>2026-10-16T14:36:03Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2397,12 +2397,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-16T14:17:38Z</t>
+          <t>2026-10-16T14:36:03Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2529,12 +2529,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-16T14:17:38Z</t>
+          <t>2026-10-16T14:36:03Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2661,12 +2661,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-16T14:17:38Z</t>
+          <t>2026-10-16T14:36:03Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-16T14:17:38Z</t>
+          <t>2026-10-16T14:36:03Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2925,12 +2925,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-16T14:17:38Z</t>
+          <t>2026-10-16T14:36:03Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3057,12 +3057,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-16T14:17:38Z</t>
+          <t>2026-10-16T14:36:03Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3189,12 +3189,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-16T14:17:38Z</t>
+          <t>2026-10-16T14:36:03Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3321,12 +3321,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-16T14:17:38Z</t>
+          <t>2026-10-16T14:36:03Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3453,12 +3453,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-16T14:17:38Z</t>
+          <t>2026-10-16T14:36:03Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3585,12 +3585,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-16T14:17:38Z</t>
+          <t>2026-10-16T14:36:03Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3717,12 +3717,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-16T14:17:38Z</t>
+          <t>2026-10-16T14:36:03Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3849,12 +3849,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-16T14:17:38Z</t>
+          <t>2026-10-16T14:36:03Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3981,12 +3981,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-16T14:17:38Z</t>
+          <t>2026-10-16T14:36:03Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -4113,12 +4113,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-16T14:17:38Z</t>
+          <t>2026-10-16T14:36:03Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>

--- a/site/exports/Tennessee_Surplus_Feed.xlsx
+++ b/site/exports/Tennessee_Surplus_Feed.xlsx
@@ -681,12 +681,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-16T14:36:03Z</t>
+          <t>2026-10-16T16:30:07Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-16T14:36:03Z</t>
+          <t>2026-10-16T16:30:07Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-16T14:36:03Z</t>
+          <t>2026-10-16T16:30:07Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-16T14:36:03Z</t>
+          <t>2026-10-16T16:30:07Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-16T14:36:03Z</t>
+          <t>2026-10-16T16:30:07Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1341,12 +1341,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-16T14:36:03Z</t>
+          <t>2026-10-16T16:30:07Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-16T14:36:03Z</t>
+          <t>2026-10-16T16:30:07Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1605,12 +1605,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-16T14:36:03Z</t>
+          <t>2026-10-16T16:30:07Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1737,12 +1737,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-16T14:36:03Z</t>
+          <t>2026-10-16T16:30:07Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1869,12 +1869,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-16T14:36:03Z</t>
+          <t>2026-10-16T16:30:07Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2001,12 +2001,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-16T14:36:03Z</t>
+          <t>2026-10-16T16:30:07Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2133,12 +2133,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-16T14:36:03Z</t>
+          <t>2026-10-16T16:30:07Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2265,12 +2265,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-16T14:36:03Z</t>
+          <t>2026-10-16T16:30:07Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2397,12 +2397,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-16T14:36:03Z</t>
+          <t>2026-10-16T16:30:07Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2529,12 +2529,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-16T14:36:03Z</t>
+          <t>2026-10-16T16:30:07Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2661,12 +2661,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-16T14:36:03Z</t>
+          <t>2026-10-16T16:30:07Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-16T14:36:03Z</t>
+          <t>2026-10-16T16:30:07Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2925,12 +2925,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-16T14:36:03Z</t>
+          <t>2026-10-16T16:30:07Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3057,12 +3057,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-16T14:36:03Z</t>
+          <t>2026-10-16T16:30:07Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3189,12 +3189,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-16T14:36:03Z</t>
+          <t>2026-10-16T16:30:07Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3321,12 +3321,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-16T14:36:03Z</t>
+          <t>2026-10-16T16:30:07Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3453,12 +3453,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-16T14:36:03Z</t>
+          <t>2026-10-16T16:30:07Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3585,12 +3585,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-16T14:36:03Z</t>
+          <t>2026-10-16T16:30:07Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3717,12 +3717,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-16T14:36:03Z</t>
+          <t>2026-10-16T16:30:07Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3849,12 +3849,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-16T14:36:03Z</t>
+          <t>2026-10-16T16:30:07Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3981,12 +3981,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-16T14:36:03Z</t>
+          <t>2026-10-16T16:30:07Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4113,12 +4113,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-16T14:36:03Z</t>
+          <t>2026-10-16T16:30:07Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>

--- a/site/exports/Tennessee_Surplus_Feed.xlsx
+++ b/site/exports/Tennessee_Surplus_Feed.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,142 +429,142 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>County</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Parcel_ID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Case_or_TaxDeed_No</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Owner_Name</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Entity_Type</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Is_Individual</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Heir_Search_Recommended</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Property_Address</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Property_Type</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Surplus_Balance_USD</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Statutory_Fee_Rate</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Est_Finder_Fee_USD</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Opportunity_Tier</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Sale_Date</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Days_Remaining_To_Claim</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Claim_Urgency_Tier</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Claim_Deadline_Date</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Statutory_Deadline_Window</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Clerk_Verification_URL</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Verify_Note</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Source_URL</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Governing_Statute</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Statute_Citation</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Record_Type</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>TYPE</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Retrieved_At</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Enriched_Timestamp</t>
         </is>
@@ -627,7 +639,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -681,12 +693,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-16T16:30:07Z</t>
+          <t>2026-10-17T10:41:35Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -759,7 +771,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -813,12 +825,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-16T16:30:07Z</t>
+          <t>2026-10-17T10:41:35Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -891,7 +903,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>-441</v>
+        <v>-442</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -945,12 +957,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-16T16:30:07Z</t>
+          <t>2026-10-17T10:41:35Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1035,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1077,12 +1089,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-16T16:30:07Z</t>
+          <t>2026-10-17T10:41:35Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1167,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1209,12 +1221,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-16T16:30:07Z</t>
+          <t>2026-10-17T10:41:35Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1299,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1341,12 +1353,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-16T16:30:07Z</t>
+          <t>2026-10-17T10:41:35Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1431,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1473,12 +1485,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-16T16:30:07Z</t>
+          <t>2026-10-17T10:41:35Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1563,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1605,12 +1617,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-16T16:30:07Z</t>
+          <t>2026-10-17T10:41:35Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1695,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1737,12 +1749,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-16T16:30:07Z</t>
+          <t>2026-10-17T10:41:35Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -1815,7 +1827,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1869,12 +1881,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-16T16:30:07Z</t>
+          <t>2026-10-17T10:41:35Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1959,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>-441</v>
+        <v>-442</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -2001,12 +2013,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-16T16:30:07Z</t>
+          <t>2026-10-17T10:41:35Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -2079,7 +2091,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2133,12 +2145,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-16T16:30:07Z</t>
+          <t>2026-10-17T10:41:35Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2223,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>-798</v>
+        <v>-799</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2265,12 +2277,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-16T16:30:07Z</t>
+          <t>2026-10-17T10:41:35Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2355,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2397,12 +2409,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-16T16:30:07Z</t>
+          <t>2026-10-17T10:41:35Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -2475,7 +2487,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>-2244</v>
+        <v>-2245</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2529,12 +2541,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-16T16:30:07Z</t>
+          <t>2026-10-17T10:41:35Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -2607,7 +2619,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>-254</v>
+        <v>-255</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2661,12 +2673,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-16T16:30:07Z</t>
+          <t>2026-10-17T10:41:35Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2751,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2793,12 +2805,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-16T16:30:07Z</t>
+          <t>2026-10-17T10:41:35Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -2871,7 +2883,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2925,12 +2937,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-16T16:30:07Z</t>
+          <t>2026-10-17T10:41:35Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -3003,7 +3015,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>-952</v>
+        <v>-953</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -3057,12 +3069,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-16T16:30:07Z</t>
+          <t>2026-10-17T10:41:35Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3147,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3189,12 +3201,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-16T16:30:07Z</t>
+          <t>2026-10-17T10:41:35Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3279,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3321,12 +3333,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-16T16:30:07Z</t>
+          <t>2026-10-17T10:41:35Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -3399,7 +3411,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>-441</v>
+        <v>-442</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3453,12 +3465,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-16T16:30:07Z</t>
+          <t>2026-10-17T10:41:35Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3543,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3585,12 +3597,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-16T16:30:07Z</t>
+          <t>2026-10-17T10:41:35Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3675,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>-203</v>
+        <v>-204</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3717,12 +3729,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-16T16:30:07Z</t>
+          <t>2026-10-17T10:41:35Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -3795,7 +3807,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>-441</v>
+        <v>-442</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -3849,12 +3861,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-16T16:30:07Z</t>
+          <t>2026-10-17T10:41:35Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3939,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>-798</v>
+        <v>-799</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3981,12 +3993,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-16T16:30:07Z</t>
+          <t>2026-10-17T10:41:35Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4071,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>-203</v>
+        <v>-204</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4113,12 +4125,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-16T16:30:07Z</t>
+          <t>2026-10-17T10:41:35Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>

--- a/site/exports/Tennessee_Surplus_Feed.xlsx
+++ b/site/exports/Tennessee_Surplus_Feed.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>24-0388-I-09402002900</t>
+          <t>24-0388-I</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -693,12 +693,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:35Z</t>
+          <t>2026-10-18T11:01:48Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>25-0490-II-072060N00100CO</t>
+          <t>25-0490-II</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -825,12 +825,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:35Z</t>
+          <t>2026-10-18T11:01:48Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>23-0416-IV-09213033100</t>
+          <t>23-0416-IV</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>-442</v>
+        <v>-443</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -957,12 +957,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:35Z</t>
+          <t>2026-10-18T11:01:48Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>24-0388-I-01816006300</t>
+          <t>24-0388-I</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:35Z</t>
+          <t>2026-10-18T11:01:48Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>25-0490-II-051150C00700CO</t>
+          <t>25-0490-II</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1221,12 +1221,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:35Z</t>
+          <t>2026-10-18T11:01:48Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>25-0490-II-051100E01800CO</t>
+          <t>25-0490-II</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1353,12 +1353,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:35Z</t>
+          <t>2026-10-18T11:01:48Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>25-0490-II-10803019800</t>
+          <t>25-0490-II</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1485,12 +1485,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:35Z</t>
+          <t>2026-10-18T11:01:48Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>25-0490-II-107130A04000CO</t>
+          <t>25-0490-II</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1617,12 +1617,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:35Z</t>
+          <t>2026-10-18T11:01:48Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>25-0490-II-043100B10200CO</t>
+          <t>25-0490-II</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1749,12 +1749,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:35Z</t>
+          <t>2026-10-18T11:01:48Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>25-0490-II-053120B03600CO</t>
+          <t>25-0490-II</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1881,12 +1881,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:35Z</t>
+          <t>2026-10-18T11:01:48Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -1908,7 +1908,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>23-0416-IV-04307003500</t>
+          <t>23-0416-IV</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1959,7 +1959,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>-442</v>
+        <v>-443</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -2013,12 +2013,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:35Z</t>
+          <t>2026-10-18T11:01:48Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>25-0490-II-053120B03500CO</t>
+          <t>25-0490-II</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2091,7 +2091,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2145,12 +2145,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:35Z</t>
+          <t>2026-10-18T11:01:48Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>22-0464-III-04900036700</t>
+          <t>22-0464-III</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>-799</v>
+        <v>-800</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2277,12 +2277,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:35Z</t>
+          <t>2026-10-18T11:01:48Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>24-0388-I-164080A04400CO</t>
+          <t>24-0388-I</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2409,12 +2409,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:35Z</t>
+          <t>2026-10-18T11:01:48Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>19-360-IV-05307008300</t>
+          <t>19-360-IV</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2487,7 +2487,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>-2245</v>
+        <v>-2246</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2541,12 +2541,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:35Z</t>
+          <t>2026-10-18T11:01:48Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>24-0388-I-08112007400</t>
+          <t>24-0388-I</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>-255</v>
+        <v>-256</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2673,12 +2673,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:35Z</t>
+          <t>2026-10-18T11:01:48Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>25-0490-II-10100020100</t>
+          <t>25-0490-II</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2805,12 +2805,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:35Z</t>
+          <t>2026-10-18T11:01:48Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>24-0388-I-14900034000</t>
+          <t>24-0388-I</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2937,12 +2937,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:35Z</t>
+          <t>2026-10-18T11:01:48Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>22-0464-III-14714018100</t>
+          <t>22-0464-III</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -3015,7 +3015,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>-953</v>
+        <v>-954</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -3069,12 +3069,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:35Z</t>
+          <t>2026-10-18T11:01:48Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>25-0490-II-01700026000</t>
+          <t>25-0490-II</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -3147,7 +3147,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3201,12 +3201,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:35Z</t>
+          <t>2026-10-18T11:01:48Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -3228,7 +3228,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>24-0388-I-02200014100</t>
+          <t>24-0388-I</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3333,12 +3333,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:35Z</t>
+          <t>2026-10-18T11:01:48Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>23-0416-IV-09413005200</t>
+          <t>23-0416-IV</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>-442</v>
+        <v>-443</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3465,12 +3465,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:35Z</t>
+          <t>2026-10-18T11:01:48Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>24-0388-I-08415005400</t>
+          <t>24-0388-I</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3543,7 +3543,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3597,12 +3597,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:35Z</t>
+          <t>2026-10-18T11:01:48Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>24-0388-I-04115010000</t>
+          <t>24-0388-I</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3675,7 +3675,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>-204</v>
+        <v>-205</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3729,12 +3729,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:35Z</t>
+          <t>2026-10-18T11:01:48Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -3756,7 +3756,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>23-0416-IV-05916016200</t>
+          <t>23-0416-IV</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3807,7 +3807,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>-442</v>
+        <v>-443</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -3861,12 +3861,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:35Z</t>
+          <t>2026-10-18T11:01:48Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>22-0464-III-12810020100</t>
+          <t>22-0464-III</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3939,7 +3939,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>-799</v>
+        <v>-800</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3993,12 +3993,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:35Z</t>
+          <t>2026-10-18T11:01:48Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>24-0388-I-03100000100</t>
+          <t>24-0388-I</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>-204</v>
+        <v>-205</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4125,12 +4125,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:35Z</t>
+          <t>2026-10-18T11:01:48Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>

--- a/site/exports/Tennessee_Surplus_Feed.xlsx
+++ b/site/exports/Tennessee_Surplus_Feed.xlsx
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -693,12 +693,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:48Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -825,12 +825,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:48Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>-443</v>
+        <v>-444</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -957,12 +957,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:48Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:48Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1221,12 +1221,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:48Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1353,12 +1353,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:48Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1485,12 +1485,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:48Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1617,12 +1617,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:48Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1749,12 +1749,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:48Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1881,12 +1881,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:48Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>-443</v>
+        <v>-444</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -2013,12 +2013,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:48Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -2091,7 +2091,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2145,12 +2145,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:48Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>-800</v>
+        <v>-801</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2277,12 +2277,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:48Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2409,12 +2409,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:48Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -2487,7 +2487,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>-2246</v>
+        <v>-2247</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2541,12 +2541,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:48Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>-256</v>
+        <v>-257</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2673,12 +2673,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:48Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2805,12 +2805,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:48Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2937,12 +2937,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:48Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -3015,7 +3015,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>-954</v>
+        <v>-955</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -3069,12 +3069,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:48Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -3147,7 +3147,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3201,12 +3201,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:48Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3333,12 +3333,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:48Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>-443</v>
+        <v>-444</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3465,12 +3465,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:48Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -3543,7 +3543,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3597,12 +3597,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:48Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>-205</v>
+        <v>-206</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3729,12 +3729,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:48Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -3807,7 +3807,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>-443</v>
+        <v>-444</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -3861,12 +3861,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:48Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -3939,7 +3939,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>-800</v>
+        <v>-801</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3993,12 +3993,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:48Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>-205</v>
+        <v>-206</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4125,12 +4125,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:48Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>

--- a/site/exports/Tennessee_Surplus_Feed.xlsx
+++ b/site/exports/Tennessee_Surplus_Feed.xlsx
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -693,12 +693,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -825,12 +825,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>-444</v>
+        <v>-445</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -957,12 +957,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1221,12 +1221,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1353,12 +1353,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1485,12 +1485,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1617,12 +1617,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1749,12 +1749,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1881,12 +1881,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>-444</v>
+        <v>-445</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -2013,12 +2013,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2091,7 +2091,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2145,12 +2145,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>-801</v>
+        <v>-802</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2277,12 +2277,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2409,12 +2409,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2487,7 +2487,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>-2247</v>
+        <v>-2248</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2541,12 +2541,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>-257</v>
+        <v>-258</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2673,12 +2673,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2805,12 +2805,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2937,12 +2937,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3015,7 +3015,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>-955</v>
+        <v>-956</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -3069,12 +3069,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3147,7 +3147,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3201,12 +3201,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3333,12 +3333,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>-444</v>
+        <v>-445</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3465,12 +3465,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3543,7 +3543,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3597,12 +3597,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>-206</v>
+        <v>-207</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3729,12 +3729,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3807,7 +3807,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>-444</v>
+        <v>-445</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -3861,12 +3861,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3939,7 +3939,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>-801</v>
+        <v>-802</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3993,12 +3993,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>-206</v>
+        <v>-207</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4125,12 +4125,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>

--- a/site/exports/Tennessee_Surplus_Feed.xlsx
+++ b/site/exports/Tennessee_Surplus_Feed.xlsx
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -693,12 +693,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-21T11:46:19Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -825,12 +825,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-21T11:46:19Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>-445</v>
+        <v>-446</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -957,12 +957,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-21T11:46:19Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-21T11:46:19Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1221,12 +1221,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-21T11:46:19Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1353,12 +1353,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-21T11:46:19Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1485,12 +1485,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-21T11:46:19Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1617,12 +1617,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-21T11:46:19Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1749,12 +1749,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-21T11:46:19Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1881,12 +1881,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-21T11:46:19Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>-445</v>
+        <v>-446</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -2013,12 +2013,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-21T11:46:19Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -2091,7 +2091,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2145,12 +2145,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-21T11:46:19Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>-802</v>
+        <v>-803</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2277,12 +2277,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-21T11:46:19Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2409,12 +2409,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-21T11:46:19Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -2487,7 +2487,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>-2248</v>
+        <v>-2249</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2541,12 +2541,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-21T11:46:19Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>-258</v>
+        <v>-259</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2673,12 +2673,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-21T11:46:19Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2805,12 +2805,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-21T11:46:19Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2937,12 +2937,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-21T11:46:19Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -3015,7 +3015,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>-956</v>
+        <v>-957</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -3069,12 +3069,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-21T11:46:19Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -3147,7 +3147,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3201,12 +3201,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-21T11:46:19Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3333,12 +3333,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-21T11:46:19Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>-445</v>
+        <v>-446</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3465,12 +3465,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-21T11:46:19Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -3543,7 +3543,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3597,12 +3597,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-21T11:46:19Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>-207</v>
+        <v>-208</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3729,12 +3729,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-21T11:46:19Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -3807,7 +3807,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>-445</v>
+        <v>-446</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -3861,12 +3861,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-21T11:46:19Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -3939,7 +3939,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>-802</v>
+        <v>-803</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3993,12 +3993,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-21T11:46:19Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>-207</v>
+        <v>-208</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4125,12 +4125,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-21T11:46:19Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>

--- a/site/exports/Tennessee_Surplus_Feed.xlsx
+++ b/site/exports/Tennessee_Surplus_Feed.xlsx
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>-23</v>
+        <v>-22</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -693,12 +693,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:19Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -825,12 +825,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:19Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>-446</v>
+        <v>-445</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -957,12 +957,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:19Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>-23</v>
+        <v>-22</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:19Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1221,12 +1221,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:19Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1353,12 +1353,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:19Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1485,12 +1485,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:19Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1617,12 +1617,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:19Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1749,12 +1749,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:19Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1881,12 +1881,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:19Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>-446</v>
+        <v>-445</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -2013,12 +2013,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:19Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2091,7 +2091,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2145,12 +2145,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:19Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>-803</v>
+        <v>-802</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2277,12 +2277,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:19Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>-23</v>
+        <v>-22</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2409,12 +2409,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:19Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2487,7 +2487,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>-2249</v>
+        <v>-2248</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2541,12 +2541,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:19Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>-259</v>
+        <v>-258</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2673,12 +2673,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:19Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2805,12 +2805,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:19Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>-23</v>
+        <v>-22</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2937,12 +2937,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:19Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3015,7 +3015,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>-957</v>
+        <v>-956</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -3069,12 +3069,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:19Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3147,7 +3147,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3201,12 +3201,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:19Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>-23</v>
+        <v>-22</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3333,12 +3333,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:19Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>-446</v>
+        <v>-445</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3465,12 +3465,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:19Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3543,7 +3543,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>-23</v>
+        <v>-22</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3597,12 +3597,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:19Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>-208</v>
+        <v>-207</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3729,12 +3729,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:19Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3807,7 +3807,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>-446</v>
+        <v>-445</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -3861,12 +3861,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:19Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3939,7 +3939,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>-803</v>
+        <v>-802</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3993,12 +3993,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:19Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>-208</v>
+        <v>-207</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4125,12 +4125,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:19Z</t>
+          <t>2026-10-20T11:33:39Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>

--- a/site/exports/Tennessee_Surplus_Feed.xlsx
+++ b/site/exports/Tennessee_Surplus_Feed.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB28"/>
+  <dimension ref="A1:AF28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -569,6 +569,26 @@
           <t>Enriched_Timestamp</t>
         </is>
       </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Owner_Name_Redacted</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>docket_id</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>parcel_id_raw</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Access_Status</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -588,12 +608,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>24-0388-I</t>
+          <t>24-0388-████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Estate and Heirs of Woodard, Helen M &amp; Pope</t>
+          <t>E. &amp; a. P████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -609,12 +629,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Parcel 09402002900, Metropolitan Nashville &amp; Davidson County, TN</t>
+          <t>Parcel 09402002900, [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Vacant Land / Acreage</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -639,7 +659,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>-22</v>
+        <v>-24</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -693,12 +713,32 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-22T09:22:42Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>E. &amp; a. P████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>24-0388-I</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>09402002900</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -720,12 +760,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>25-0490-II</t>
+          <t>25-0490-████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Marckwardt, Thomas Hunter &amp; Kimberly P</t>
+          <t>M. &amp; T. P████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -741,12 +781,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Parcel 072060N00100CO, Metropolitan Nashville &amp; Davidson County, TN</t>
+          <t>Parcel 072060N00100CO, [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Vacant Land / Acreage</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -771,7 +811,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -825,12 +865,32 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-22T09:22:42Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>M. &amp; T. P████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>25-0490-II</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>072060N00100CO</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -852,12 +912,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>23-0416-IV</t>
+          <t>23-0416-████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mayes, Charles E.</t>
+          <t>M. &amp; C. E████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -873,12 +933,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Parcel 09213033100, Metropolitan Nashville &amp; Davidson County, TN</t>
+          <t>Parcel 09213033100, [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Vacant Land / Acreage</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -903,7 +963,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>-445</v>
+        <v>-447</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -957,12 +1017,32 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-22T09:22:42Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>M. &amp; C. E████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>23-0416-IV</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>09213033100</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -984,12 +1064,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>24-0388-I</t>
+          <t>24-0388-████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Estate and Heirs of Parker, Randall</t>
+          <t>E. &amp; a. R██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1005,12 +1085,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Parcel 01816006300, Metropolitan Nashville &amp; Davidson County, TN</t>
+          <t>Parcel 01816006300, [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Vacant Land / Acreage</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -1035,7 +1115,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>-22</v>
+        <v>-24</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1089,12 +1169,32 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-22T09:22:42Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>E. &amp; a. R██████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>24-0388-I</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>01816006300</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1216,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>25-0490-II</t>
+          <t>25-0490-████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Wallace, Melissa</t>
+          <t>W. &amp; M. M██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1137,12 +1237,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Parcel 051150C00700CO, Metropolitan Nashville &amp; Davidson County, TN</t>
+          <t>Parcel 051150C00700CO, [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Vacant Land / Acreage</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -1167,7 +1267,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1221,12 +1321,32 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-22T09:22:42Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>W. &amp; M. M██████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>25-0490-II</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>051150C00700CO</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1368,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>25-0490-II</t>
+          <t>25-0490-████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gupton, Marsha E</t>
+          <t>G. &amp; M. E████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1269,12 +1389,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Parcel 051100E01800CO, Metropolitan Nashville &amp; Davidson County, TN</t>
+          <t>Parcel 051100E01800CO, [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Vacant Land / Acreage</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -1299,7 +1419,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1353,12 +1473,32 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-22T09:22:42Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>G. &amp; M. E████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>25-0490-II</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>051100E01800CO</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1520,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>25-0490-II</t>
+          <t>25-0490-████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Raisane, Thomas D. &amp; Pennington, Deborah</t>
+          <t>R. &amp; T. D██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1401,12 +1541,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Parcel 10803019800, Metropolitan Nashville &amp; Davidson County, TN</t>
+          <t>Parcel 10803019800, [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Vacant Land / Acreage</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -1431,7 +1571,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1485,12 +1625,32 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-22T09:22:42Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>R. &amp; T. D██████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>25-0490-II</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>10803019800</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -1512,12 +1672,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>25-0490-II</t>
+          <t>25-0490-████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Manning, Walter &amp; Delilah &amp; Karah J</t>
+          <t>M. &amp; W. J████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1533,12 +1693,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Parcel 107130A04000CO, Metropolitan Nashville &amp; Davidson County, TN</t>
+          <t>Parcel 107130A04000CO, [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Vacant Land / Acreage</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1563,7 +1723,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1617,12 +1777,32 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-22T09:22:42Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>M. &amp; W. J████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>25-0490-II</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>107130A04000CO</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1824,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>25-0490-II</t>
+          <t>25-0490-████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>McClain, Eugenia</t>
+          <t>M. &amp; E. E██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1665,12 +1845,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Parcel 043100B10200CO, Metropolitan Nashville &amp; Davidson County, TN</t>
+          <t>Parcel 043100B10200CO, [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Vacant Land / Acreage</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1695,7 +1875,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1749,12 +1929,32 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-22T09:22:42Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>M. &amp; E. E██████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>25-0490-II</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>043100B10200CO</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -1776,12 +1976,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>25-0490-II</t>
+          <t>25-0490-████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Amin, Siddharth</t>
+          <t>A. &amp; S. S████████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1797,12 +1997,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Parcel 053120B03600CO, Metropolitan Nashville &amp; Davidson County, TN</t>
+          <t>Parcel 053120B03600CO, [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Vacant Land / Acreage</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1827,7 +2027,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1881,12 +2081,32 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-22T09:22:42Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>A. &amp; S. S████████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>25-0490-II</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>053120B03600CO</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -1908,12 +2128,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>23-0416-IV</t>
+          <t>23-0416-████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Estate and Heirs of Maynard, Brownie Lee</t>
+          <t>E. &amp; a. L████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1929,12 +2149,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Parcel 04307003500, Metropolitan Nashville &amp; Davidson County, TN</t>
+          <t>Parcel 04307003500, [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Vacant Land / Acreage</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1959,7 +2179,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>-445</v>
+        <v>-447</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -2013,12 +2233,32 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-22T09:22:42Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>E. &amp; a. L████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>23-0416-IV</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>04307003500</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -2040,12 +2280,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>25-0490-II</t>
+          <t>25-0490-████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Amin, Siddharth</t>
+          <t>A. &amp; S. S████████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2061,12 +2301,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Parcel 053120B03500CO, Metropolitan Nashville &amp; Davidson County, TN</t>
+          <t>Parcel 053120B03500CO, [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Vacant Land / Acreage</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -2091,7 +2331,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2145,12 +2385,32 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-22T09:22:42Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>A. &amp; S. S████████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>25-0490-II</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>053120B03500CO</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -2172,12 +2432,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>22-0464-III</t>
+          <t>22-0464-████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Estate and Heirs of Meadows, James A &amp; Onether I.</t>
+          <t>E. &amp; a. I████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2193,12 +2453,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Parcel 04900036700, Metropolitan Nashville &amp; Davidson County, TN</t>
+          <t>Parcel 04900036700, [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Vacant Land / Acreage</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -2223,7 +2483,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>-802</v>
+        <v>-804</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2277,12 +2537,32 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-22T09:22:42Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>E. &amp; a. I████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>22-0464-III</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>04900036700</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -2304,12 +2584,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>24-0388-I</t>
+          <t>24-0388-████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Infinity Home Builders, G.P.</t>
+          <t>I. &amp; H. G████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2325,12 +2605,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Parcel 164080A04400CO, Metropolitan Nashville &amp; Davidson County, TN</t>
+          <t>Parcel 164080A04400CO, [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Vacant Land / Acreage</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -2355,7 +2635,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>-22</v>
+        <v>-24</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2409,12 +2689,32 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-22T09:22:42Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>I. &amp; H. G████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>24-0388-I</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>164080A04400CO</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2736,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>19-360-IV</t>
+          <t>19-360-████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Weatherford, Harry Jr.</t>
+          <t>W. &amp; H. J████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2457,12 +2757,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Parcel 05307008300, Metropolitan Nashville &amp; Davidson County, TN</t>
+          <t>Parcel 05307008300, [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Vacant Land / Acreage</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -2487,7 +2787,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>-2248</v>
+        <v>-2250</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2541,12 +2841,32 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-22T09:22:42Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>W. &amp; H. J████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>19-360-IV</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>05307008300</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -2568,12 +2888,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>24-0388-I</t>
+          <t>24-0388-████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stratton, Debra A</t>
+          <t>S. &amp; D. A████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2589,12 +2909,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Parcel 08112007400, Metropolitan Nashville &amp; Davidson County, TN</t>
+          <t>Parcel 08112007400, [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Vacant Land / Acreage</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -2619,7 +2939,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>-258</v>
+        <v>-260</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2673,12 +2993,32 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-22T09:22:42Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>S. &amp; D. A████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>24-0388-I</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>08112007400</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -2700,12 +3040,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>25-0490-II</t>
+          <t>25-0490-████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Williams, Searra &amp; Lindsley, Marquita</t>
+          <t>W. &amp; S. M███████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2721,12 +3061,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Parcel 10100020100, Metropolitan Nashville &amp; Davidson County, TN</t>
+          <t>Parcel 10100020100, [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Vacant Land / Acreage</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -2751,7 +3091,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2805,12 +3145,32 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-22T09:22:42Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>W. &amp; S. M███████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>25-0490-II</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>10100020100</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -2832,12 +3192,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>24-0388-I</t>
+          <t>24-0388-████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Zaver, Vinod T &amp; Manglaben, V</t>
+          <t>Z. &amp; V. V████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2853,12 +3213,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Parcel 14900034000, Metropolitan Nashville &amp; Davidson County, TN</t>
+          <t>Parcel 14900034000, [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Vacant Land / Acreage</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -2883,7 +3243,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>-22</v>
+        <v>-24</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2937,12 +3297,32 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-22T09:22:42Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Z. &amp; V. V████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>24-0388-I</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>14900034000</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -2964,12 +3344,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>22-0464-III</t>
+          <t>22-0464-████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sundance of Nashville LTD</t>
+          <t>S. &amp; o. L████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2985,12 +3365,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Parcel 14714018100, Metropolitan Nashville &amp; Davidson County, TN</t>
+          <t>Parcel 14714018100, [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Vacant Land / Acreage</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -3015,7 +3395,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>-956</v>
+        <v>-958</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -3069,12 +3449,32 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-22T09:22:42Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>S. &amp; o. L████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>22-0464-III</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>14714018100</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -3096,12 +3496,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>25-0490-II</t>
+          <t>25-0490-████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Davis, Jeanette (Le) &amp; Davis, Tyson</t>
+          <t>D. &amp; J. T████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3117,12 +3517,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Parcel 01700026000, Metropolitan Nashville &amp; Davidson County, TN</t>
+          <t>Parcel 01700026000, [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Vacant Land / Acreage</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -3147,7 +3547,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3201,12 +3601,32 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-22T09:22:42Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>D. &amp; J. T████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>25-0490-II</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>01700026000</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3648,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>24-0388-I</t>
+          <t>24-0388-████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Davidson, Genevieve Ann</t>
+          <t>D. &amp; G. A████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -3249,12 +3669,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Parcel 02200014100, Metropolitan Nashville &amp; Davidson County, TN</t>
+          <t>Parcel 02200014100, [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Vacant Land / Acreage</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -3279,7 +3699,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>-22</v>
+        <v>-24</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3333,12 +3753,32 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-22T09:22:42Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>D. &amp; G. A████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>24-0388-I</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>02200014100</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -3360,12 +3800,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>23-0416-IV</t>
+          <t>23-0416-████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Estate and Heirs of Howse, Margaret L</t>
+          <t>E. &amp; a. L████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3381,12 +3821,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Parcel 09413005200, Metropolitan Nashville &amp; Davidson County, TN</t>
+          <t>Parcel 09413005200, [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Vacant Land / Acreage</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -3411,7 +3851,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>-445</v>
+        <v>-447</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3465,12 +3905,32 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-22T09:22:42Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>E. &amp; a. L████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>23-0416-IV</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>09413005200</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -3492,12 +3952,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>24-0388-I</t>
+          <t>24-0388-████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Estate and Heirs of Martin, William J et ux</t>
+          <t>E. &amp; a. u████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3513,12 +3973,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Parcel 08415005400, Metropolitan Nashville &amp; Davidson County, TN</t>
+          <t>Parcel 08415005400, [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Vacant Land / Acreage</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -3543,7 +4003,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>-22</v>
+        <v>-24</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3597,12 +4057,32 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-22T09:22:42Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>E. &amp; a. u████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>24-0388-I</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>08415005400</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -3624,12 +4104,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>24-0388-I</t>
+          <t>24-0388-████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Estate &amp; Heirs of England, Linda &amp; Lee, Fredda</t>
+          <t>E. &amp; H. F█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3645,12 +4125,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Parcel 04115010000, Metropolitan Nashville &amp; Davidson County, TN</t>
+          <t>Parcel 04115010000, [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Vacant Land / Acreage</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -3675,7 +4155,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>-207</v>
+        <v>-209</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3729,12 +4209,32 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-22T09:22:42Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>E. &amp; H. F█████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>24-0388-I</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>04115010000</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -3756,12 +4256,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>23-0416-IV</t>
+          <t>23-0416-████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Mims, James V. &amp; Olene H.</t>
+          <t>M. &amp; J. H████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3777,12 +4277,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Parcel 05916016200, Metropolitan Nashville &amp; Davidson County, TN</t>
+          <t>Parcel 05916016200, [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Vacant Land / Acreage</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -3807,7 +4307,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>-445</v>
+        <v>-447</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -3861,12 +4361,32 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-22T09:22:42Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>M. &amp; J. H████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>23-0416-IV</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>05916016200</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -3888,12 +4408,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>22-0464-III</t>
+          <t>22-0464-████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rainey, Kenneth &amp; Ross, Linda</t>
+          <t>R. &amp; K. L████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3909,12 +4429,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Parcel 12810020100, Metropolitan Nashville &amp; Davidson County, TN</t>
+          <t>Parcel 12810020100, [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Vacant Land / Acreage</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -3939,7 +4459,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>-802</v>
+        <v>-804</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3993,12 +4513,32 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-22T09:22:42Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>R. &amp; K. L████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>22-0464-III</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>12810020100</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -4020,12 +4560,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>24-0388-I</t>
+          <t>24-0388-████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hobson, Albert</t>
+          <t>H. &amp; A. A█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -4041,12 +4581,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Parcel 03100000100, Metropolitan Nashville &amp; Davidson County, TN</t>
+          <t>Parcel 03100000100, [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Vacant Land / Acreage</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -4071,7 +4611,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>-207</v>
+        <v>-209</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4125,12 +4665,32 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:39Z</t>
+          <t>2026-10-22T09:22:42Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>H. &amp; A. A█████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>24-0388-I</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>03100000100</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>

--- a/site/exports/Tennessee_Surplus_Feed.xlsx
+++ b/site/exports/Tennessee_Surplus_Feed.xlsx
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:57Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -865,12 +865,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:57Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>-447</v>
+        <v>-448</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -1017,12 +1017,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:57Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:57Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:57Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:57Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:57Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:57Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1929,12 +1929,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:57Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -2081,12 +2081,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:57Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>-447</v>
+        <v>-448</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:57Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2385,12 +2385,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:57Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>-804</v>
+        <v>-805</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:57Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2689,12 +2689,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:57Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>-2250</v>
+        <v>-2251</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2841,12 +2841,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:57Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>-260</v>
+        <v>-261</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:57Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -3145,12 +3145,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:57Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -3297,12 +3297,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:57Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>-958</v>
+        <v>-959</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -3449,12 +3449,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:57Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3547,7 +3547,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3601,12 +3601,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:57Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3699,7 +3699,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3753,12 +3753,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:57Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3851,7 +3851,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>-447</v>
+        <v>-448</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3905,12 +3905,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:57Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -4057,12 +4057,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:57Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -4155,7 +4155,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>-209</v>
+        <v>-210</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -4209,12 +4209,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:57Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -4307,7 +4307,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>-447</v>
+        <v>-448</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -4361,12 +4361,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:57Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4459,7 +4459,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>-804</v>
+        <v>-805</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:57Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>-209</v>
+        <v>-210</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4665,12 +4665,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:57Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">

--- a/site/exports/Tennessee_Surplus_Feed.xlsx
+++ b/site/exports/Tennessee_Surplus_Feed.xlsx
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:57Z</t>
+          <t>2026-10-24T08:50:37Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -865,12 +865,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:57Z</t>
+          <t>2026-10-24T08:50:37Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>-448</v>
+        <v>-449</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -1017,12 +1017,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:57Z</t>
+          <t>2026-10-24T08:50:37Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:57Z</t>
+          <t>2026-10-24T08:50:37Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:57Z</t>
+          <t>2026-10-24T08:50:37Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:57Z</t>
+          <t>2026-10-24T08:50:37Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:57Z</t>
+          <t>2026-10-24T08:50:37Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:57Z</t>
+          <t>2026-10-24T08:50:37Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1929,12 +1929,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:57Z</t>
+          <t>2026-10-24T08:50:37Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -2081,12 +2081,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:57Z</t>
+          <t>2026-10-24T08:50:37Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>-448</v>
+        <v>-449</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:57Z</t>
+          <t>2026-10-24T08:50:37Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2385,12 +2385,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:57Z</t>
+          <t>2026-10-24T08:50:37Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>-805</v>
+        <v>-806</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:57Z</t>
+          <t>2026-10-24T08:50:37Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2689,12 +2689,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:57Z</t>
+          <t>2026-10-24T08:50:37Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>-2251</v>
+        <v>-2252</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2841,12 +2841,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:57Z</t>
+          <t>2026-10-24T08:50:37Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>-261</v>
+        <v>-262</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:57Z</t>
+          <t>2026-10-24T08:50:37Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -3145,12 +3145,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:57Z</t>
+          <t>2026-10-24T08:50:37Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -3297,12 +3297,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:57Z</t>
+          <t>2026-10-24T08:50:37Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>-959</v>
+        <v>-960</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -3449,12 +3449,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:57Z</t>
+          <t>2026-10-24T08:50:37Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3547,7 +3547,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3601,12 +3601,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:57Z</t>
+          <t>2026-10-24T08:50:37Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3699,7 +3699,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3753,12 +3753,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:57Z</t>
+          <t>2026-10-24T08:50:37Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3851,7 +3851,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>-448</v>
+        <v>-449</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3905,12 +3905,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:57Z</t>
+          <t>2026-10-24T08:50:37Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -4057,12 +4057,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:57Z</t>
+          <t>2026-10-24T08:50:37Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -4155,7 +4155,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>-210</v>
+        <v>-211</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -4209,12 +4209,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:57Z</t>
+          <t>2026-10-24T08:50:37Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -4307,7 +4307,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>-448</v>
+        <v>-449</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -4361,12 +4361,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:57Z</t>
+          <t>2026-10-24T08:50:37Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4459,7 +4459,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>-805</v>
+        <v>-806</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:57Z</t>
+          <t>2026-10-24T08:50:37Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>-210</v>
+        <v>-211</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4665,12 +4665,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:57Z</t>
+          <t>2026-10-24T08:50:37Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">

--- a/site/exports/Tennessee_Surplus_Feed.xlsx
+++ b/site/exports/Tennessee_Surplus_Feed.xlsx
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:37Z</t>
+          <t>2026-10-25T09:07:21Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -865,12 +865,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:37Z</t>
+          <t>2026-10-25T09:07:21Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>-449</v>
+        <v>-450</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -1017,12 +1017,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:37Z</t>
+          <t>2026-10-25T09:07:21Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:37Z</t>
+          <t>2026-10-25T09:07:21Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:37Z</t>
+          <t>2026-10-25T09:07:21Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:37Z</t>
+          <t>2026-10-25T09:07:21Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:37Z</t>
+          <t>2026-10-25T09:07:21Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:37Z</t>
+          <t>2026-10-25T09:07:21Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1929,12 +1929,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:37Z</t>
+          <t>2026-10-25T09:07:21Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -2081,12 +2081,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:37Z</t>
+          <t>2026-10-25T09:07:21Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>-449</v>
+        <v>-450</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:37Z</t>
+          <t>2026-10-25T09:07:21Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2385,12 +2385,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:37Z</t>
+          <t>2026-10-25T09:07:21Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>-806</v>
+        <v>-807</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:37Z</t>
+          <t>2026-10-25T09:07:21Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2689,12 +2689,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:37Z</t>
+          <t>2026-10-25T09:07:21Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>-2252</v>
+        <v>-2253</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2841,12 +2841,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:37Z</t>
+          <t>2026-10-25T09:07:21Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>-262</v>
+        <v>-263</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:37Z</t>
+          <t>2026-10-25T09:07:21Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -3145,12 +3145,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:37Z</t>
+          <t>2026-10-25T09:07:21Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -3297,12 +3297,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:37Z</t>
+          <t>2026-10-25T09:07:21Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>-960</v>
+        <v>-961</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -3449,12 +3449,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:37Z</t>
+          <t>2026-10-25T09:07:21Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3547,7 +3547,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3601,12 +3601,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:37Z</t>
+          <t>2026-10-25T09:07:21Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3699,7 +3699,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3753,12 +3753,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:37Z</t>
+          <t>2026-10-25T09:07:21Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3851,7 +3851,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>-449</v>
+        <v>-450</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3905,12 +3905,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:37Z</t>
+          <t>2026-10-25T09:07:21Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -4057,12 +4057,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:37Z</t>
+          <t>2026-10-25T09:07:21Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -4155,7 +4155,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>-211</v>
+        <v>-212</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -4209,12 +4209,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:37Z</t>
+          <t>2026-10-25T09:07:21Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -4307,7 +4307,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>-449</v>
+        <v>-450</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -4361,12 +4361,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:37Z</t>
+          <t>2026-10-25T09:07:21Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4459,7 +4459,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>-806</v>
+        <v>-807</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:37Z</t>
+          <t>2026-10-25T09:07:21Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>-211</v>
+        <v>-212</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4665,12 +4665,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:37Z</t>
+          <t>2026-10-25T09:07:21Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">

--- a/site/exports/Tennessee_Surplus_Feed.xlsx
+++ b/site/exports/Tennessee_Surplus_Feed.xlsx
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:21Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -865,12 +865,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:21Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>-450</v>
+        <v>-451</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -1017,12 +1017,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:21Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:21Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:21Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:21Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:21Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:21Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1929,12 +1929,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:21Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -2081,12 +2081,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:21Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>-450</v>
+        <v>-451</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:21Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2385,12 +2385,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:21Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>-807</v>
+        <v>-808</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:21Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2689,12 +2689,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:21Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>-2253</v>
+        <v>-2254</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2841,12 +2841,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:21Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>-263</v>
+        <v>-264</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:21Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -3145,12 +3145,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:21Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -3297,12 +3297,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:21Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>-961</v>
+        <v>-962</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -3449,12 +3449,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:21Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3547,7 +3547,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3601,12 +3601,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:21Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3699,7 +3699,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3753,12 +3753,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:21Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3851,7 +3851,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>-450</v>
+        <v>-451</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3905,12 +3905,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:21Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -4057,12 +4057,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:21Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -4155,7 +4155,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>-212</v>
+        <v>-213</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -4209,12 +4209,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:21Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -4307,7 +4307,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>-450</v>
+        <v>-451</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -4361,12 +4361,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:21Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4459,7 +4459,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>-807</v>
+        <v>-808</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:21Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>-212</v>
+        <v>-213</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4665,12 +4665,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:21Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">

--- a/site/exports/Tennessee_Surplus_Feed.xlsx
+++ b/site/exports/Tennessee_Surplus_Feed.xlsx
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:11Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -865,12 +865,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:11Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>-451</v>
+        <v>-452</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -1017,12 +1017,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:11Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:11Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:11Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:11Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:11Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:11Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1929,12 +1929,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:11Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -2081,12 +2081,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:11Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>-451</v>
+        <v>-452</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:11Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2385,12 +2385,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:11Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>-808</v>
+        <v>-809</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:11Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2689,12 +2689,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:11Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>-2254</v>
+        <v>-2255</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2841,12 +2841,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:11Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>-264</v>
+        <v>-265</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:11Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -3145,12 +3145,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:11Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -3297,12 +3297,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:11Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>-962</v>
+        <v>-963</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -3449,12 +3449,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:11Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3547,7 +3547,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3601,12 +3601,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:11Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3699,7 +3699,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3753,12 +3753,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:11Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3851,7 +3851,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>-451</v>
+        <v>-452</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3905,12 +3905,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:11Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -4057,12 +4057,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:11Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -4155,7 +4155,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>-213</v>
+        <v>-214</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -4209,12 +4209,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:11Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -4307,7 +4307,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>-451</v>
+        <v>-452</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -4361,12 +4361,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:11Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4459,7 +4459,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>-808</v>
+        <v>-809</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:11Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>-213</v>
+        <v>-214</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4665,12 +4665,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:11Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">

--- a/site/exports/Tennessee_Surplus_Feed.xlsx
+++ b/site/exports/Tennessee_Surplus_Feed.xlsx
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>-29</v>
+        <v>-30</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:11Z</t>
+          <t>2026-10-28T10:32:09Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -865,12 +865,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:11Z</t>
+          <t>2026-10-28T10:32:09Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>-452</v>
+        <v>-453</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -1017,12 +1017,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:11Z</t>
+          <t>2026-10-28T10:32:09Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>-29</v>
+        <v>-30</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:11Z</t>
+          <t>2026-10-28T10:32:09Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:11Z</t>
+          <t>2026-10-28T10:32:09Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:11Z</t>
+          <t>2026-10-28T10:32:09Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:11Z</t>
+          <t>2026-10-28T10:32:09Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:11Z</t>
+          <t>2026-10-28T10:32:09Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1929,12 +1929,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:11Z</t>
+          <t>2026-10-28T10:32:09Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -2081,12 +2081,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:11Z</t>
+          <t>2026-10-28T10:32:09Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>-452</v>
+        <v>-453</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:11Z</t>
+          <t>2026-10-28T10:32:09Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2385,12 +2385,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:11Z</t>
+          <t>2026-10-28T10:32:09Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>-809</v>
+        <v>-810</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:11Z</t>
+          <t>2026-10-28T10:32:09Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>-29</v>
+        <v>-30</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2689,12 +2689,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:11Z</t>
+          <t>2026-10-28T10:32:09Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>-2255</v>
+        <v>-2256</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2841,12 +2841,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:11Z</t>
+          <t>2026-10-28T10:32:09Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>-265</v>
+        <v>-266</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:11Z</t>
+          <t>2026-10-28T10:32:09Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -3145,12 +3145,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:11Z</t>
+          <t>2026-10-28T10:32:09Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>-29</v>
+        <v>-30</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -3297,12 +3297,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:11Z</t>
+          <t>2026-10-28T10:32:09Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>-963</v>
+        <v>-964</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -3449,12 +3449,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:11Z</t>
+          <t>2026-10-28T10:32:09Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3547,7 +3547,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3601,12 +3601,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:11Z</t>
+          <t>2026-10-28T10:32:09Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3699,7 +3699,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>-29</v>
+        <v>-30</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3753,12 +3753,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:11Z</t>
+          <t>2026-10-28T10:32:09Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3851,7 +3851,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>-452</v>
+        <v>-453</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3905,12 +3905,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:11Z</t>
+          <t>2026-10-28T10:32:09Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>-29</v>
+        <v>-30</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -4057,12 +4057,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:11Z</t>
+          <t>2026-10-28T10:32:09Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -4155,7 +4155,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>-214</v>
+        <v>-215</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -4209,12 +4209,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:11Z</t>
+          <t>2026-10-28T10:32:09Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -4307,7 +4307,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>-452</v>
+        <v>-453</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -4361,12 +4361,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:11Z</t>
+          <t>2026-10-28T10:32:09Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4459,7 +4459,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>-809</v>
+        <v>-810</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:11Z</t>
+          <t>2026-10-28T10:32:09Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>-214</v>
+        <v>-215</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4665,12 +4665,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:11Z</t>
+          <t>2026-10-28T10:32:09Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">

--- a/site/exports/Tennessee_Surplus_Feed.xlsx
+++ b/site/exports/Tennessee_Surplus_Feed.xlsx
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>-30</v>
+        <v>-31</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:09Z</t>
+          <t>2026-10-29T10:51:38Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -865,12 +865,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:09Z</t>
+          <t>2026-10-29T10:51:38Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>-453</v>
+        <v>-454</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -1017,12 +1017,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:09Z</t>
+          <t>2026-10-29T10:51:38Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>-30</v>
+        <v>-31</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:09Z</t>
+          <t>2026-10-29T10:51:38Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:09Z</t>
+          <t>2026-10-29T10:51:38Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:09Z</t>
+          <t>2026-10-29T10:51:38Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:09Z</t>
+          <t>2026-10-29T10:51:38Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:09Z</t>
+          <t>2026-10-29T10:51:38Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1929,12 +1929,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:09Z</t>
+          <t>2026-10-29T10:51:38Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -2081,12 +2081,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:09Z</t>
+          <t>2026-10-29T10:51:38Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>-453</v>
+        <v>-454</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:09Z</t>
+          <t>2026-10-29T10:51:38Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2385,12 +2385,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:09Z</t>
+          <t>2026-10-29T10:51:38Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>-810</v>
+        <v>-811</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:09Z</t>
+          <t>2026-10-29T10:51:38Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>-30</v>
+        <v>-31</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2689,12 +2689,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:09Z</t>
+          <t>2026-10-29T10:51:38Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>-2256</v>
+        <v>-2257</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2841,12 +2841,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:09Z</t>
+          <t>2026-10-29T10:51:38Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>-266</v>
+        <v>-267</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:09Z</t>
+          <t>2026-10-29T10:51:38Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -3145,12 +3145,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:09Z</t>
+          <t>2026-10-29T10:51:38Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>-30</v>
+        <v>-31</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -3297,12 +3297,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:09Z</t>
+          <t>2026-10-29T10:51:38Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>-964</v>
+        <v>-965</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -3449,12 +3449,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:09Z</t>
+          <t>2026-10-29T10:51:38Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3547,7 +3547,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3601,12 +3601,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:09Z</t>
+          <t>2026-10-29T10:51:38Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3699,7 +3699,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>-30</v>
+        <v>-31</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3753,12 +3753,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:09Z</t>
+          <t>2026-10-29T10:51:38Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3851,7 +3851,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>-453</v>
+        <v>-454</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3905,12 +3905,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:09Z</t>
+          <t>2026-10-29T10:51:38Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>-30</v>
+        <v>-31</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -4057,12 +4057,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:09Z</t>
+          <t>2026-10-29T10:51:38Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -4155,7 +4155,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>-215</v>
+        <v>-216</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -4209,12 +4209,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:09Z</t>
+          <t>2026-10-29T10:51:38Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -4307,7 +4307,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>-453</v>
+        <v>-454</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -4361,12 +4361,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:09Z</t>
+          <t>2026-10-29T10:51:38Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4459,7 +4459,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>-810</v>
+        <v>-811</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:09Z</t>
+          <t>2026-10-29T10:51:38Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>-215</v>
+        <v>-216</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4665,12 +4665,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:09Z</t>
+          <t>2026-10-29T10:51:38Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">

--- a/site/exports/Tennessee_Surplus_Feed.xlsx
+++ b/site/exports/Tennessee_Surplus_Feed.xlsx
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>-31</v>
+        <v>-32</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:38Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -865,12 +865,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:38Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>-454</v>
+        <v>-455</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -1017,12 +1017,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:38Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>-31</v>
+        <v>-32</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:38Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:38Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:38Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:38Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:38Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1929,12 +1929,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:38Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -2081,12 +2081,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:38Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>-454</v>
+        <v>-455</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:38Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2385,12 +2385,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:38Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>-811</v>
+        <v>-812</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:38Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>-31</v>
+        <v>-32</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2689,12 +2689,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:38Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>-2257</v>
+        <v>-2258</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2841,12 +2841,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:38Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>-267</v>
+        <v>-268</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:38Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -3145,12 +3145,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:38Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>-31</v>
+        <v>-32</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -3297,12 +3297,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:38Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>-965</v>
+        <v>-966</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -3449,12 +3449,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:38Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3547,7 +3547,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3601,12 +3601,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:38Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3699,7 +3699,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>-31</v>
+        <v>-32</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3753,12 +3753,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:38Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3851,7 +3851,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>-454</v>
+        <v>-455</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3905,12 +3905,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:38Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>-31</v>
+        <v>-32</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -4057,12 +4057,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:38Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -4155,7 +4155,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>-216</v>
+        <v>-217</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -4209,12 +4209,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:38Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -4307,7 +4307,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>-454</v>
+        <v>-455</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -4361,12 +4361,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:38Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4459,7 +4459,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>-811</v>
+        <v>-812</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:38Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>-216</v>
+        <v>-217</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4665,12 +4665,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:38Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">

--- a/site/exports/Tennessee_Surplus_Feed.xlsx
+++ b/site/exports/Tennessee_Surplus_Feed.xlsx
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>-32</v>
+        <v>-33</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:10Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -865,12 +865,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:10Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>-455</v>
+        <v>-456</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -1017,12 +1017,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:10Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>-32</v>
+        <v>-33</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:10Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:10Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:10Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:10Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:10Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1929,12 +1929,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:10Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -2081,12 +2081,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:10Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>-455</v>
+        <v>-456</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:10Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2385,12 +2385,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:10Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>-812</v>
+        <v>-813</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:10Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>-32</v>
+        <v>-33</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2689,12 +2689,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:10Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>-2258</v>
+        <v>-2259</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2841,12 +2841,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:10Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>-268</v>
+        <v>-269</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:10Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -3145,12 +3145,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:10Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>-32</v>
+        <v>-33</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -3297,12 +3297,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:10Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>-966</v>
+        <v>-967</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -3449,12 +3449,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:10Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3547,7 +3547,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3601,12 +3601,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:10Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3699,7 +3699,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>-32</v>
+        <v>-33</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3753,12 +3753,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:10Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3851,7 +3851,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>-455</v>
+        <v>-456</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3905,12 +3905,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:10Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>-32</v>
+        <v>-33</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -4057,12 +4057,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:10Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -4155,7 +4155,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>-217</v>
+        <v>-218</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -4209,12 +4209,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:10Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -4307,7 +4307,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>-455</v>
+        <v>-456</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -4361,12 +4361,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:10Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4459,7 +4459,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>-812</v>
+        <v>-813</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:10Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>-217</v>
+        <v>-218</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4665,12 +4665,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:10Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
